--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127778808</v>
+        <v>127778779</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>91332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,39 +1699,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568222</v>
+        <v>568208</v>
       </c>
       <c r="R11" t="n">
-        <v>7084851</v>
+        <v>7084856</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127778779</v>
+        <v>127778808</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,34 +1806,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568208</v>
+        <v>568222</v>
       </c>
       <c r="R12" t="n">
-        <v>7084856</v>
+        <v>7084851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2014,57 +2014,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127777006</v>
+        <v>127774579</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567977</v>
+        <v>567972</v>
       </c>
       <c r="R14" t="n">
-        <v>7084799</v>
+        <v>7084896</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2093,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,52 +2107,71 @@
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127774579</v>
+        <v>127777006</v>
       </c>
       <c r="B15" t="n">
-        <v>78779</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567972</v>
+        <v>567977</v>
       </c>
       <c r="R15" t="n">
-        <v>7084896</v>
+        <v>7084799</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2190,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2200,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,12 +2225,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2568,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777269</v>
+        <v>127777376</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,37 +2589,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568024</v>
+        <v>568017</v>
       </c>
       <c r="R19" t="n">
-        <v>7084724</v>
+        <v>7084676</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2638,7 +2653,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2648,7 +2663,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,36 +2681,46 @@
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127778829</v>
+        <v>127777269</v>
       </c>
       <c r="B20" t="n">
-        <v>97327</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2700,13 +2730,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568221</v>
+        <v>568024</v>
       </c>
       <c r="R20" t="n">
-        <v>7084843</v>
+        <v>7084724</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2735,7 +2765,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2745,7 +2775,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,62 +2790,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127777376</v>
+        <v>127778829</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>97327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568017</v>
+        <v>568221</v>
       </c>
       <c r="R21" t="n">
-        <v>7084676</v>
+        <v>7084843</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2857,12 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3005,50 +3025,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127778496</v>
+        <v>127778786</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>98471</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568144</v>
+        <v>568210</v>
       </c>
       <c r="R23" t="n">
-        <v>7084832</v>
+        <v>7084862</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3080,7 +3095,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3090,12 +3105,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3122,45 +3132,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127778786</v>
+        <v>127778496</v>
       </c>
       <c r="B24" t="n">
-        <v>98471</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568210</v>
+        <v>568144</v>
       </c>
       <c r="R24" t="n">
-        <v>7084862</v>
+        <v>7084832</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,7 +3207,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3202,7 +3217,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,6 +3342,16 @@
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ella-Paulina Åhrén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ella-Paulina Åhrén</t>
+        </is>
+      </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127777166</v>
       </c>
       <c r="B2" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127774723</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>127774278</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>127775069</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127778779</v>
+        <v>127778808</v>
       </c>
       <c r="B11" t="n">
-        <v>91332</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,34 +1699,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568208</v>
+        <v>568222</v>
       </c>
       <c r="R11" t="n">
-        <v>7084856</v>
+        <v>7084851</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,50 +1800,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127778808</v>
+        <v>127779918</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>92628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568222</v>
+        <v>568105</v>
       </c>
       <c r="R12" t="n">
-        <v>7084851</v>
+        <v>7084785</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,32 +1907,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127779918</v>
+        <v>127778779</v>
       </c>
       <c r="B13" t="n">
-        <v>92622</v>
+        <v>91338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568105</v>
+        <v>568208</v>
       </c>
       <c r="R13" t="n">
-        <v>7084785</v>
+        <v>7084856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,48 +2014,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127774579</v>
+        <v>127777006</v>
       </c>
       <c r="B14" t="n">
-        <v>78779</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567972</v>
+        <v>567977</v>
       </c>
       <c r="R14" t="n">
-        <v>7084896</v>
+        <v>7084799</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,69 +2118,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127777006</v>
+        <v>127774579</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567977</v>
+        <v>567972</v>
       </c>
       <c r="R15" t="n">
-        <v>7084799</v>
+        <v>7084896</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,12 +2225,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2357,7 +2357,7 @@
         <v>127774340</v>
       </c>
       <c r="B17" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>127778829</v>
       </c>
       <c r="B21" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>127778736</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3025,45 +3025,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127778786</v>
+        <v>127778496</v>
       </c>
       <c r="B23" t="n">
-        <v>98471</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568210</v>
+        <v>568144</v>
       </c>
       <c r="R23" t="n">
-        <v>7084862</v>
+        <v>7084832</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3095,7 +3100,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3105,7 +3110,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3132,50 +3142,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127778496</v>
+        <v>127778786</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>98477</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568144</v>
+        <v>568210</v>
       </c>
       <c r="R24" t="n">
-        <v>7084832</v>
+        <v>7084862</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3207,7 +3212,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3217,12 +3222,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127777215</v>
+        <v>127779099</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,37 +3260,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568021</v>
+        <v>568259</v>
       </c>
       <c r="R25" t="n">
-        <v>7084739</v>
+        <v>7084847</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3319,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,22 +3354,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127779099</v>
+        <v>127777215</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,42 +3377,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568259</v>
+        <v>568021</v>
       </c>
       <c r="R26" t="n">
-        <v>7084847</v>
+        <v>7084739</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3431,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3441,12 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127777166</v>
       </c>
       <c r="B2" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127774276</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>127778509</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>127774904</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127774723</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>127774278</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>127775069</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>127774875</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>127778350</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127778808</v>
+        <v>127778779</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>91341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,39 +1699,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568222</v>
+        <v>568208</v>
       </c>
       <c r="R11" t="n">
-        <v>7084851</v>
+        <v>7084856</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1798,7 @@
         <v>127779918</v>
       </c>
       <c r="B12" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127778779</v>
+        <v>127778808</v>
       </c>
       <c r="B13" t="n">
-        <v>91338</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,34 +1913,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568208</v>
+        <v>568222</v>
       </c>
       <c r="R13" t="n">
-        <v>7084856</v>
+        <v>7084851</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,57 +2014,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127777006</v>
+        <v>127774579</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>78782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567977</v>
+        <v>567972</v>
       </c>
       <c r="R14" t="n">
-        <v>7084799</v>
+        <v>7084896</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2093,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,60 +2109,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127774579</v>
+        <v>127777006</v>
       </c>
       <c r="B15" t="n">
-        <v>78779</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567972</v>
+        <v>567977</v>
       </c>
       <c r="R15" t="n">
-        <v>7084896</v>
+        <v>7084799</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,12 +2225,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2240,7 +2240,7 @@
         <v>127777452</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>127774340</v>
       </c>
       <c r="B17" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>127780066</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777376</v>
+        <v>127777269</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2589,42 +2589,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568017</v>
+        <v>568024</v>
       </c>
       <c r="R19" t="n">
-        <v>7084676</v>
+        <v>7084724</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2653,7 +2648,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2663,12 +2658,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,22 +2673,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777269</v>
+        <v>127777376</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,37 +2696,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568024</v>
+        <v>568017</v>
       </c>
       <c r="R20" t="n">
-        <v>7084724</v>
+        <v>7084676</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2765,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2775,7 +2770,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,12 +2790,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
         <v>127778829</v>
       </c>
       <c r="B21" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>127778736</v>
       </c>
       <c r="B22" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>127778496</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>127778786</v>
       </c>
       <c r="B24" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127779099</v>
+        <v>127777215</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>80126</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,42 +3260,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568259</v>
+        <v>568021</v>
       </c>
       <c r="R25" t="n">
-        <v>7084847</v>
+        <v>7084739</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,22 +3344,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127777215</v>
+        <v>127779099</v>
       </c>
       <c r="B26" t="n">
-        <v>80123</v>
+        <v>57666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3377,37 +3367,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568021</v>
+        <v>568259</v>
       </c>
       <c r="R26" t="n">
-        <v>7084739</v>
+        <v>7084847</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3431,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3441,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127777166</v>
       </c>
       <c r="B2" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127774276</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>127778509</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>127774904</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127774723</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>127774278</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,42 +1358,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127775069</v>
+        <v>127778350</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,13 +1398,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567949</v>
+        <v>568041</v>
       </c>
       <c r="R8" t="n">
-        <v>7084881</v>
+        <v>7084861</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,9 +1431,24 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,12 +1463,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1467,7 +1478,7 @@
         <v>127774875</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,38 +1582,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778350</v>
+        <v>127775069</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1611,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568041</v>
+        <v>567949</v>
       </c>
       <c r="R10" t="n">
-        <v>7084861</v>
+        <v>7084881</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,24 +1659,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,12 +1676,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
         <v>127778779</v>
       </c>
       <c r="B11" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>127779918</v>
       </c>
       <c r="B12" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>127778808</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,48 +2014,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127774579</v>
+        <v>127777006</v>
       </c>
       <c r="B14" t="n">
-        <v>78782</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567972</v>
+        <v>567977</v>
       </c>
       <c r="R14" t="n">
-        <v>7084896</v>
+        <v>7084799</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,69 +2118,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127777006</v>
+        <v>127774579</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>78788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567977</v>
+        <v>567972</v>
       </c>
       <c r="R15" t="n">
-        <v>7084799</v>
+        <v>7084896</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,12 +2225,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2240,7 +2240,7 @@
         <v>127777452</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,45 +2354,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127774340</v>
+        <v>127780066</v>
       </c>
       <c r="B17" t="n">
-        <v>97336</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567969</v>
+        <v>568032</v>
       </c>
       <c r="R17" t="n">
-        <v>7084911</v>
+        <v>7084920</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,7 +2429,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2434,7 +2439,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,62 +2459,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127780066</v>
+        <v>127774340</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>97344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568032</v>
+        <v>567969</v>
       </c>
       <c r="R18" t="n">
-        <v>7084920</v>
+        <v>7084911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2536,7 +2541,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2546,12 +2551,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,22 +2566,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777269</v>
+        <v>127777376</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2589,37 +2589,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568024</v>
+        <v>568017</v>
       </c>
       <c r="R19" t="n">
-        <v>7084724</v>
+        <v>7084676</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2648,7 +2653,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2658,7 +2663,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,22 +2683,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777376</v>
+        <v>127777269</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,42 +2706,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568017</v>
+        <v>568024</v>
       </c>
       <c r="R20" t="n">
-        <v>7084676</v>
+        <v>7084724</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2765,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,12 +2775,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,12 +2790,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
         <v>127778829</v>
       </c>
       <c r="B21" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>127778736</v>
       </c>
       <c r="B22" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>127778496</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>127778786</v>
       </c>
       <c r="B24" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127777215</v>
       </c>
       <c r="B25" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127779099</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127777166</v>
       </c>
       <c r="B2" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127774723</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>127774278</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778350</v>
+        <v>127774875</v>
       </c>
       <c r="B8" t="n">
         <v>57672</v>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568041</v>
+        <v>567939</v>
       </c>
       <c r="R8" t="n">
-        <v>7084861</v>
+        <v>7084890</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,19 +1431,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:43</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1463,19 +1453,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127774875</v>
+        <v>127778350</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1515,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567939</v>
+        <v>568041</v>
       </c>
       <c r="R9" t="n">
-        <v>7084890</v>
+        <v>7084861</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,9 +1538,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1570,12 +1570,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
         <v>127775069</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>127778779</v>
       </c>
       <c r="B11" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,45 +1795,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127779918</v>
+        <v>127778808</v>
       </c>
       <c r="B12" t="n">
-        <v>92639</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568105</v>
+        <v>568222</v>
       </c>
       <c r="R12" t="n">
-        <v>7084785</v>
+        <v>7084851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,50 +1907,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127778808</v>
+        <v>127779918</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>92640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568222</v>
+        <v>568105</v>
       </c>
       <c r="R13" t="n">
-        <v>7084851</v>
+        <v>7084785</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,57 +2014,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127777006</v>
+        <v>127774579</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>78788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567977</v>
+        <v>567972</v>
       </c>
       <c r="R14" t="n">
-        <v>7084799</v>
+        <v>7084896</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2093,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,60 +2109,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127774579</v>
+        <v>127777006</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567972</v>
+        <v>567977</v>
       </c>
       <c r="R15" t="n">
-        <v>7084896</v>
+        <v>7084799</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,12 +2225,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2474,7 +2474,7 @@
         <v>127774340</v>
       </c>
       <c r="B18" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777376</v>
+        <v>127777269</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2589,42 +2589,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568017</v>
+        <v>568024</v>
       </c>
       <c r="R19" t="n">
-        <v>7084676</v>
+        <v>7084724</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2653,7 +2648,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2663,12 +2658,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,22 +2673,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777269</v>
+        <v>127777376</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,37 +2696,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568024</v>
+        <v>568017</v>
       </c>
       <c r="R20" t="n">
-        <v>7084724</v>
+        <v>7084676</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2765,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2775,7 +2770,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,12 +2790,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
         <v>127778829</v>
       </c>
       <c r="B21" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>127778736</v>
       </c>
       <c r="B22" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>127778786</v>
       </c>
       <c r="B24" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127777215</v>
+        <v>127779099</v>
       </c>
       <c r="B25" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,37 +3260,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568021</v>
+        <v>568259</v>
       </c>
       <c r="R25" t="n">
-        <v>7084739</v>
+        <v>7084847</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3319,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,22 +3354,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127779099</v>
+        <v>127777215</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,42 +3377,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568259</v>
+        <v>568021</v>
       </c>
       <c r="R26" t="n">
-        <v>7084847</v>
+        <v>7084739</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3431,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3441,12 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -1358,38 +1358,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127774875</v>
+        <v>127775069</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1398,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567939</v>
+        <v>567949</v>
       </c>
       <c r="R8" t="n">
-        <v>7084890</v>
+        <v>7084881</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1434,11 +1438,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127778350</v>
+        <v>127774875</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1505,13 +1504,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568041</v>
+        <v>567939</v>
       </c>
       <c r="R9" t="n">
-        <v>7084861</v>
+        <v>7084890</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,19 +1537,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:43</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1570,54 +1559,50 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127775069</v>
+        <v>127778350</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1626,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567949</v>
+        <v>568041</v>
       </c>
       <c r="R10" t="n">
-        <v>7084881</v>
+        <v>7084861</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,9 +1644,24 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,12 +1676,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1795,50 +1795,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127778808</v>
+        <v>127779918</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>92640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568222</v>
+        <v>568105</v>
       </c>
       <c r="R12" t="n">
-        <v>7084851</v>
+        <v>7084785</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,45 +1902,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127779918</v>
+        <v>127778808</v>
       </c>
       <c r="B13" t="n">
-        <v>92640</v>
+        <v>57669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568105</v>
+        <v>568222</v>
       </c>
       <c r="R13" t="n">
-        <v>7084785</v>
+        <v>7084851</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,48 +2014,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127774579</v>
+        <v>127777006</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567972</v>
+        <v>567977</v>
       </c>
       <c r="R14" t="n">
-        <v>7084896</v>
+        <v>7084799</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,69 +2118,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127777006</v>
+        <v>127774579</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>78788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567977</v>
+        <v>567972</v>
       </c>
       <c r="R15" t="n">
-        <v>7084799</v>
+        <v>7084896</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,12 +2225,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2578,32 +2578,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777269</v>
+        <v>127778829</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>97345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568024</v>
+        <v>568221</v>
       </c>
       <c r="R19" t="n">
-        <v>7084724</v>
+        <v>7084843</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,22 +2673,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777376</v>
+        <v>127777269</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,42 +2696,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568017</v>
+        <v>568024</v>
       </c>
       <c r="R20" t="n">
-        <v>7084676</v>
+        <v>7084724</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2755,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,12 +2765,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,57 +2780,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127778829</v>
+        <v>127777376</v>
       </c>
       <c r="B21" t="n">
-        <v>97345</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568221</v>
+        <v>568017</v>
       </c>
       <c r="R21" t="n">
-        <v>7084843</v>
+        <v>7084676</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2867,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2877,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127779099</v>
+        <v>127777215</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,42 +3260,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568259</v>
+        <v>568021</v>
       </c>
       <c r="R25" t="n">
-        <v>7084847</v>
+        <v>7084739</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,22 +3344,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127777215</v>
+        <v>127779099</v>
       </c>
       <c r="B26" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3377,37 +3367,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568021</v>
+        <v>568259</v>
       </c>
       <c r="R26" t="n">
-        <v>7084739</v>
+        <v>7084847</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3431,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3441,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127777166</v>
       </c>
       <c r="B2" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127774723</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>127774278</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,42 +1358,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127775069</v>
+        <v>127774875</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567949</v>
+        <v>567939</v>
       </c>
       <c r="R8" t="n">
-        <v>7084881</v>
+        <v>7084890</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1438,6 +1434,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1465,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127774875</v>
+        <v>127778350</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1504,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567939</v>
+        <v>568041</v>
       </c>
       <c r="R9" t="n">
-        <v>7084890</v>
+        <v>7084861</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,9 +1538,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1559,50 +1570,54 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778350</v>
+        <v>127775069</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1611,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568041</v>
+        <v>567949</v>
       </c>
       <c r="R10" t="n">
-        <v>7084861</v>
+        <v>7084881</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,24 +1659,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,12 +1676,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
         <v>127778779</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,45 +1795,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127779918</v>
+        <v>127778808</v>
       </c>
       <c r="B12" t="n">
-        <v>92640</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568105</v>
+        <v>568222</v>
       </c>
       <c r="R12" t="n">
-        <v>7084785</v>
+        <v>7084851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,50 +1907,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127778808</v>
+        <v>127779918</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>92641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568222</v>
+        <v>568105</v>
       </c>
       <c r="R13" t="n">
-        <v>7084851</v>
+        <v>7084785</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,7 +2017,7 @@
         <v>127777006</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>127774340</v>
       </c>
       <c r="B18" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>127778829</v>
       </c>
       <c r="B19" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>127778736</v>
       </c>
       <c r="B22" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>127778786</v>
       </c>
       <c r="B24" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127777166</v>
       </c>
       <c r="B2" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127774723</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>127774278</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,38 +1358,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127774875</v>
+        <v>127775069</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1398,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567939</v>
+        <v>567949</v>
       </c>
       <c r="R8" t="n">
-        <v>7084890</v>
+        <v>7084881</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1434,11 +1438,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127778350</v>
+        <v>127774875</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1505,13 +1504,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568041</v>
+        <v>567939</v>
       </c>
       <c r="R9" t="n">
-        <v>7084861</v>
+        <v>7084890</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,19 +1537,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:43</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1570,54 +1559,50 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127775069</v>
+        <v>127778350</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1626,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567949</v>
+        <v>568041</v>
       </c>
       <c r="R10" t="n">
-        <v>7084881</v>
+        <v>7084861</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,9 +1644,24 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,22 +1676,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127778779</v>
+        <v>127778808</v>
       </c>
       <c r="B11" t="n">
-        <v>91351</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,34 +1699,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568208</v>
+        <v>568222</v>
       </c>
       <c r="R11" t="n">
-        <v>7084856</v>
+        <v>7084851</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127778808</v>
+        <v>127778779</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>91352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,39 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568222</v>
+        <v>568208</v>
       </c>
       <c r="R12" t="n">
-        <v>7084851</v>
+        <v>7084856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,7 +1910,7 @@
         <v>127779918</v>
       </c>
       <c r="B13" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>127777006</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>127774340</v>
       </c>
       <c r="B18" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,32 +2578,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127778829</v>
+        <v>127777269</v>
       </c>
       <c r="B19" t="n">
-        <v>97346</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568221</v>
+        <v>568024</v>
       </c>
       <c r="R19" t="n">
-        <v>7084843</v>
+        <v>7084724</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,22 +2673,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777269</v>
+        <v>127777376</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,37 +2696,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568024</v>
+        <v>568017</v>
       </c>
       <c r="R20" t="n">
-        <v>7084724</v>
+        <v>7084676</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2755,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2765,7 +2770,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,62 +2790,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127777376</v>
+        <v>127778829</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>97347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568017</v>
+        <v>568221</v>
       </c>
       <c r="R21" t="n">
-        <v>7084676</v>
+        <v>7084843</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2867,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2877,12 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,7 +2912,7 @@
         <v>127778736</v>
       </c>
       <c r="B22" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3025,50 +3025,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127778496</v>
+        <v>127778786</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>98491</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568144</v>
+        <v>568210</v>
       </c>
       <c r="R23" t="n">
-        <v>7084832</v>
+        <v>7084862</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,7 +3095,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3110,12 +3105,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,45 +3132,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127778786</v>
+        <v>127778496</v>
       </c>
       <c r="B24" t="n">
-        <v>98490</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568210</v>
+        <v>568144</v>
       </c>
       <c r="R24" t="n">
-        <v>7084862</v>
+        <v>7084832</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3212,7 +3207,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3222,7 +3217,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127777215</v>
+        <v>127779099</v>
       </c>
       <c r="B25" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,37 +3260,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568021</v>
+        <v>568259</v>
       </c>
       <c r="R25" t="n">
-        <v>7084739</v>
+        <v>7084847</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3319,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,22 +3354,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127779099</v>
+        <v>127777215</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,42 +3377,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568259</v>
+        <v>568021</v>
       </c>
       <c r="R26" t="n">
-        <v>7084847</v>
+        <v>7084739</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3431,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3441,12 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -1358,42 +1358,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127775069</v>
+        <v>127774875</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567949</v>
+        <v>567939</v>
       </c>
       <c r="R8" t="n">
-        <v>7084881</v>
+        <v>7084890</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1438,6 +1434,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1465,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127774875</v>
+        <v>127778350</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1504,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567939</v>
+        <v>568041</v>
       </c>
       <c r="R9" t="n">
-        <v>7084890</v>
+        <v>7084861</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,9 +1538,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1559,50 +1570,54 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778350</v>
+        <v>127775069</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1611,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568041</v>
+        <v>567949</v>
       </c>
       <c r="R10" t="n">
-        <v>7084861</v>
+        <v>7084881</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,24 +1659,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,62 +1676,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127778808</v>
+        <v>127779918</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>92642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568222</v>
+        <v>568105</v>
       </c>
       <c r="R11" t="n">
-        <v>7084851</v>
+        <v>7084785</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1907,45 +1902,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127779918</v>
+        <v>127778808</v>
       </c>
       <c r="B13" t="n">
-        <v>92642</v>
+        <v>57669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568105</v>
+        <v>568222</v>
       </c>
       <c r="R13" t="n">
-        <v>7084785</v>
+        <v>7084851</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3025,45 +3025,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127778786</v>
+        <v>127778496</v>
       </c>
       <c r="B23" t="n">
-        <v>98491</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568210</v>
+        <v>568144</v>
       </c>
       <c r="R23" t="n">
-        <v>7084862</v>
+        <v>7084832</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3095,7 +3100,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3105,7 +3110,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3132,50 +3142,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127778496</v>
+        <v>127778786</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>98491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568144</v>
+        <v>568210</v>
       </c>
       <c r="R24" t="n">
-        <v>7084832</v>
+        <v>7084862</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3207,7 +3212,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3217,12 +3222,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127779099</v>
+        <v>127777215</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,42 +3260,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568259</v>
+        <v>568021</v>
       </c>
       <c r="R25" t="n">
-        <v>7084847</v>
+        <v>7084739</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,22 +3344,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127777215</v>
+        <v>127779099</v>
       </c>
       <c r="B26" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3377,37 +3367,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568021</v>
+        <v>568259</v>
       </c>
       <c r="R26" t="n">
-        <v>7084739</v>
+        <v>7084847</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3431,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3441,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -2578,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777269</v>
+        <v>127777376</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2589,37 +2589,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568024</v>
+        <v>568017</v>
       </c>
       <c r="R19" t="n">
-        <v>7084724</v>
+        <v>7084676</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2648,7 +2653,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2658,7 +2663,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,22 +2683,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777376</v>
+        <v>127777269</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,42 +2706,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568017</v>
+        <v>568024</v>
       </c>
       <c r="R20" t="n">
-        <v>7084676</v>
+        <v>7084724</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2765,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,12 +2775,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,12 +2790,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3025,50 +3025,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127778496</v>
+        <v>127778786</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>98491</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568144</v>
+        <v>568210</v>
       </c>
       <c r="R23" t="n">
-        <v>7084832</v>
+        <v>7084862</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,7 +3095,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3110,12 +3105,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,45 +3132,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127778786</v>
+        <v>127778496</v>
       </c>
       <c r="B24" t="n">
-        <v>98491</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568210</v>
+        <v>568144</v>
       </c>
       <c r="R24" t="n">
-        <v>7084862</v>
+        <v>7084832</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3212,7 +3207,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3222,7 +3217,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -3025,45 +3025,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127778786</v>
+        <v>127778496</v>
       </c>
       <c r="B23" t="n">
-        <v>98491</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568210</v>
+        <v>568144</v>
       </c>
       <c r="R23" t="n">
-        <v>7084862</v>
+        <v>7084832</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3095,7 +3100,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3105,7 +3110,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3132,50 +3142,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127778496</v>
+        <v>127778786</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>98491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568144</v>
+        <v>568210</v>
       </c>
       <c r="R24" t="n">
-        <v>7084832</v>
+        <v>7084862</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3207,7 +3212,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3217,12 +3222,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127777215</v>
+        <v>127779099</v>
       </c>
       <c r="B25" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,37 +3260,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568021</v>
+        <v>568259</v>
       </c>
       <c r="R25" t="n">
-        <v>7084739</v>
+        <v>7084847</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3319,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,22 +3354,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127779099</v>
+        <v>127777215</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,42 +3377,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568259</v>
+        <v>568021</v>
       </c>
       <c r="R26" t="n">
-        <v>7084847</v>
+        <v>7084739</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3431,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3441,12 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127779099</v>
+        <v>127777215</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,42 +3260,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568259</v>
+        <v>568021</v>
       </c>
       <c r="R25" t="n">
-        <v>7084847</v>
+        <v>7084739</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,22 +3344,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127777215</v>
+        <v>127779099</v>
       </c>
       <c r="B26" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3377,37 +3367,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568021</v>
+        <v>568259</v>
       </c>
       <c r="R26" t="n">
-        <v>7084739</v>
+        <v>7084847</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3431,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3441,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -2578,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777376</v>
+        <v>127777269</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2589,42 +2589,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568017</v>
+        <v>568024</v>
       </c>
       <c r="R19" t="n">
-        <v>7084676</v>
+        <v>7084724</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2653,7 +2648,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2663,12 +2658,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,22 +2673,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777269</v>
+        <v>127777376</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,37 +2696,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568024</v>
+        <v>568017</v>
       </c>
       <c r="R20" t="n">
-        <v>7084724</v>
+        <v>7084676</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2765,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2775,7 +2770,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,12 +2790,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127777166</v>
       </c>
       <c r="B2" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127774276</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>127778509</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>127774904</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127774723</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>127774278</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,38 +1358,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127774875</v>
+        <v>127775069</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1398,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567939</v>
+        <v>567949</v>
       </c>
       <c r="R8" t="n">
-        <v>7084890</v>
+        <v>7084881</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1434,11 +1438,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127778350</v>
+        <v>127774875</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,13 +1504,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568041</v>
+        <v>567939</v>
       </c>
       <c r="R9" t="n">
-        <v>7084861</v>
+        <v>7084890</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,19 +1537,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:43</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1570,54 +1559,50 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127775069</v>
+        <v>127778350</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1626,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567949</v>
+        <v>568041</v>
       </c>
       <c r="R10" t="n">
-        <v>7084881</v>
+        <v>7084861</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,9 +1644,24 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,12 +1676,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
         <v>127779918</v>
       </c>
       <c r="B11" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127778779</v>
+        <v>127778808</v>
       </c>
       <c r="B12" t="n">
-        <v>91352</v>
+        <v>57670</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,34 +1806,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568208</v>
+        <v>568222</v>
       </c>
       <c r="R12" t="n">
-        <v>7084856</v>
+        <v>7084851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127778808</v>
+        <v>127778779</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>91360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,39 +1918,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568222</v>
+        <v>568208</v>
       </c>
       <c r="R13" t="n">
-        <v>7084851</v>
+        <v>7084856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,57 +2014,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127777006</v>
+        <v>127774579</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>78791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567977</v>
+        <v>567972</v>
       </c>
       <c r="R14" t="n">
-        <v>7084799</v>
+        <v>7084896</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2093,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,60 +2109,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127774579</v>
+        <v>127777006</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567972</v>
+        <v>567977</v>
       </c>
       <c r="R15" t="n">
-        <v>7084896</v>
+        <v>7084799</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,12 +2225,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2240,7 +2240,7 @@
         <v>127777452</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,50 +2354,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127780066</v>
+        <v>127774340</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>97355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568032</v>
+        <v>567969</v>
       </c>
       <c r="R17" t="n">
-        <v>7084920</v>
+        <v>7084911</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,7 +2424,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2439,12 +2434,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,57 +2449,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127774340</v>
+        <v>127780066</v>
       </c>
       <c r="B18" t="n">
-        <v>97347</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567969</v>
+        <v>568032</v>
       </c>
       <c r="R18" t="n">
-        <v>7084911</v>
+        <v>7084920</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,7 +2536,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2551,7 +2546,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,12 +2566,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2581,7 +2581,7 @@
         <v>127777269</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127777376</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>127778829</v>
       </c>
       <c r="B21" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>127778736</v>
       </c>
       <c r="B22" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>127778496</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>127778786</v>
       </c>
       <c r="B24" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127779099</v>
+        <v>127777215</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>80135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,42 +3260,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568259</v>
+        <v>568021</v>
       </c>
       <c r="R25" t="n">
-        <v>7084847</v>
+        <v>7084739</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,22 +3344,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127777215</v>
+        <v>127779099</v>
       </c>
       <c r="B26" t="n">
-        <v>80132</v>
+        <v>57673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3377,37 +3367,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568021</v>
+        <v>568259</v>
       </c>
       <c r="R26" t="n">
-        <v>7084739</v>
+        <v>7084847</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3431,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3441,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -1688,32 +1688,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127779918</v>
+        <v>127778779</v>
       </c>
       <c r="B11" t="n">
-        <v>92650</v>
+        <v>91360</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568105</v>
+        <v>568208</v>
       </c>
       <c r="R11" t="n">
-        <v>7084785</v>
+        <v>7084856</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,50 +1795,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127778808</v>
+        <v>127779918</v>
       </c>
       <c r="B12" t="n">
-        <v>57670</v>
+        <v>92650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568222</v>
+        <v>568105</v>
       </c>
       <c r="R12" t="n">
-        <v>7084851</v>
+        <v>7084785</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127778779</v>
+        <v>127778808</v>
       </c>
       <c r="B13" t="n">
-        <v>91360</v>
+        <v>57670</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,34 +1913,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568208</v>
+        <v>568222</v>
       </c>
       <c r="R13" t="n">
-        <v>7084856</v>
+        <v>7084851</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127777166</v>
       </c>
       <c r="B2" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127774276</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>127778509</v>
       </c>
       <c r="B4" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>127774904</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127774723</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>127774278</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,42 +1358,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127775069</v>
+        <v>127774875</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567949</v>
+        <v>567939</v>
       </c>
       <c r="R8" t="n">
-        <v>7084881</v>
+        <v>7084890</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1438,6 +1434,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127774875</v>
+        <v>127778350</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567939</v>
+        <v>568041</v>
       </c>
       <c r="R9" t="n">
-        <v>7084890</v>
+        <v>7084861</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,9 +1538,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1559,50 +1570,54 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778350</v>
+        <v>127775069</v>
       </c>
       <c r="B10" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1611,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568041</v>
+        <v>567949</v>
       </c>
       <c r="R10" t="n">
-        <v>7084861</v>
+        <v>7084881</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,24 +1659,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,12 +1676,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
         <v>127778779</v>
       </c>
       <c r="B11" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>127779918</v>
       </c>
       <c r="B12" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>127778808</v>
       </c>
       <c r="B13" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,48 +2014,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127774579</v>
+        <v>127777006</v>
       </c>
       <c r="B14" t="n">
-        <v>78791</v>
+        <v>98571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567972</v>
+        <v>567977</v>
       </c>
       <c r="R14" t="n">
-        <v>7084896</v>
+        <v>7084799</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,69 +2118,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127777006</v>
+        <v>127774579</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>78841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567977</v>
+        <v>567972</v>
       </c>
       <c r="R15" t="n">
-        <v>7084799</v>
+        <v>7084896</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,12 +2225,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2240,7 +2240,7 @@
         <v>127777452</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>127774340</v>
       </c>
       <c r="B17" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>127780066</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>127777269</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127777376</v>
       </c>
       <c r="B20" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>127778829</v>
       </c>
       <c r="B21" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>127778736</v>
       </c>
       <c r="B22" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>127778496</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>127778786</v>
       </c>
       <c r="B24" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127777215</v>
       </c>
       <c r="B25" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127779099</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -2014,57 +2014,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127777006</v>
+        <v>127774579</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>78841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567977</v>
+        <v>567972</v>
       </c>
       <c r="R14" t="n">
-        <v>7084799</v>
+        <v>7084896</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2093,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,60 +2109,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127774579</v>
+        <v>127777006</v>
       </c>
       <c r="B15" t="n">
-        <v>78841</v>
+        <v>98571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567972</v>
+        <v>567977</v>
       </c>
       <c r="R15" t="n">
-        <v>7084896</v>
+        <v>7084799</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,12 +2225,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2354,45 +2354,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127774340</v>
+        <v>127780066</v>
       </c>
       <c r="B17" t="n">
-        <v>97448</v>
+        <v>57685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567969</v>
+        <v>568032</v>
       </c>
       <c r="R17" t="n">
-        <v>7084911</v>
+        <v>7084920</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,7 +2429,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2434,7 +2439,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,62 +2459,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127780066</v>
+        <v>127774340</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>97448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568032</v>
+        <v>567969</v>
       </c>
       <c r="R18" t="n">
-        <v>7084920</v>
+        <v>7084911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2536,7 +2541,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2546,12 +2551,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,22 +2566,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777269</v>
+        <v>127777376</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2589,37 +2589,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568024</v>
+        <v>568017</v>
       </c>
       <c r="R19" t="n">
-        <v>7084724</v>
+        <v>7084676</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2648,7 +2653,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2658,7 +2663,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,22 +2683,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777376</v>
+        <v>127777269</v>
       </c>
       <c r="B20" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,42 +2706,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568017</v>
+        <v>568024</v>
       </c>
       <c r="R20" t="n">
-        <v>7084676</v>
+        <v>7084724</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2765,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,12 +2775,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,12 +2790,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127777215</v>
+        <v>127779099</v>
       </c>
       <c r="B25" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,37 +3260,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568021</v>
+        <v>568259</v>
       </c>
       <c r="R25" t="n">
-        <v>7084739</v>
+        <v>7084847</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3319,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,22 +3354,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127779099</v>
+        <v>127777215</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,42 +3377,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568259</v>
+        <v>568021</v>
       </c>
       <c r="R26" t="n">
-        <v>7084847</v>
+        <v>7084739</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3431,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3441,12 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127777166</v>
+        <v>127778779</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568005</v>
+        <v>568208</v>
       </c>
       <c r="R2" t="n">
-        <v>7084751</v>
+        <v>7084856</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127774276</v>
+        <v>127775120</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568015</v>
+        <v>567931</v>
       </c>
       <c r="R3" t="n">
-        <v>7084904</v>
+        <v>7084867</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127778509</v>
+        <v>127779918</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,51 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568143</v>
+        <v>568105</v>
       </c>
       <c r="R4" t="n">
-        <v>7084828</v>
+        <v>7084785</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127774904</v>
+        <v>127775305</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567938</v>
+        <v>567912</v>
       </c>
       <c r="R5" t="n">
-        <v>7084892</v>
+        <v>7084890</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127774723</v>
+        <v>127777269</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,43 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567958</v>
+        <v>568024</v>
       </c>
       <c r="R6" t="n">
-        <v>7084872</v>
+        <v>7084724</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1223,9 +1171,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127774278</v>
+        <v>127779776</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,46 +1221,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567964</v>
+        <v>568133</v>
       </c>
       <c r="R7" t="n">
-        <v>7084885</v>
+        <v>7084737</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,9 +1278,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,22 +1305,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127774875</v>
+        <v>127775221</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,42 +1328,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567939</v>
+        <v>567931</v>
       </c>
       <c r="R8" t="n">
-        <v>7084890</v>
+        <v>7084859</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,14 +1385,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,22 +1412,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127778350</v>
+        <v>127777215</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,42 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568041</v>
+        <v>568021</v>
       </c>
       <c r="R9" t="n">
-        <v>7084861</v>
+        <v>7084739</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,54 +1519,50 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127775069</v>
+        <v>127778808</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1626,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567949</v>
+        <v>568222</v>
       </c>
       <c r="R10" t="n">
-        <v>7084881</v>
+        <v>7084851</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,9 +1604,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,22 +1631,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127778779</v>
+        <v>127774276</v>
       </c>
       <c r="B11" t="n">
-        <v>91452</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,34 +1654,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568208</v>
+        <v>568015</v>
       </c>
       <c r="R11" t="n">
-        <v>7084856</v>
+        <v>7084904</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1728,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,48 +1760,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127779918</v>
+        <v>127774875</v>
       </c>
       <c r="B12" t="n">
-        <v>92742</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568105</v>
+        <v>567939</v>
       </c>
       <c r="R12" t="n">
-        <v>7084785</v>
+        <v>7084890</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1863,19 +1833,14 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:06</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,22 +1855,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127778808</v>
+        <v>127774904</v>
       </c>
       <c r="B13" t="n">
-        <v>57682</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,16 +1878,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1933,7 +1898,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1942,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568222</v>
+        <v>567938</v>
       </c>
       <c r="R13" t="n">
-        <v>7084851</v>
+        <v>7084892</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1952,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127774579</v>
+        <v>127777308</v>
       </c>
       <c r="B14" t="n">
-        <v>78841</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,34 +1995,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567972</v>
+        <v>568013</v>
       </c>
       <c r="R14" t="n">
-        <v>7084896</v>
+        <v>7084681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2069,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,42 +2101,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127777006</v>
+        <v>127777376</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2165,13 +2141,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567977</v>
+        <v>568017</v>
       </c>
       <c r="R15" t="n">
-        <v>7084799</v>
+        <v>7084676</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2176,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2186,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,12 +2206,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2240,7 +2221,7 @@
         <v>127777452</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127780066</v>
+        <v>127778350</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568032</v>
+        <v>568041</v>
       </c>
       <c r="R17" t="n">
-        <v>7084920</v>
+        <v>7084861</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2439,12 +2420,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,57 +2440,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127774340</v>
+        <v>127778496</v>
       </c>
       <c r="B18" t="n">
-        <v>97448</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567969</v>
+        <v>568144</v>
       </c>
       <c r="R18" t="n">
-        <v>7084911</v>
+        <v>7084832</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2551,7 +2537,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2578,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777376</v>
+        <v>127779099</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568017</v>
+        <v>568259</v>
       </c>
       <c r="R19" t="n">
-        <v>7084676</v>
+        <v>7084847</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,7 +2644,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2663,7 +2654,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2695,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777269</v>
+        <v>127780066</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,37 +2697,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568024</v>
+        <v>568032</v>
       </c>
       <c r="R20" t="n">
-        <v>7084724</v>
+        <v>7084920</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2765,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2775,7 +2771,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,60 +2791,74 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127778829</v>
+        <v>127778509</v>
       </c>
       <c r="B21" t="n">
-        <v>97448</v>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568221</v>
+        <v>568143</v>
       </c>
       <c r="R21" t="n">
-        <v>7084843</v>
+        <v>7084828</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2872,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2909,54 +2924,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127778736</v>
+        <v>127775383</v>
       </c>
       <c r="B22" t="n">
-        <v>91470</v>
+        <v>99035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568186</v>
+        <v>567906</v>
       </c>
       <c r="R22" t="n">
-        <v>7084850</v>
+        <v>7084891</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2998,7 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,50 +3031,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127778496</v>
+        <v>127779879</v>
       </c>
       <c r="B23" t="n">
-        <v>57685</v>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568144</v>
+        <v>568163</v>
       </c>
       <c r="R23" t="n">
-        <v>7084832</v>
+        <v>7084797</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,7 +3101,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3110,12 +3111,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3130,60 +3126,69 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127778786</v>
+        <v>127774278</v>
       </c>
       <c r="B24" t="n">
-        <v>98592</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568210</v>
+        <v>567964</v>
       </c>
       <c r="R24" t="n">
-        <v>7084862</v>
+        <v>7084885</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3210,19 +3215,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,50 +3232,54 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127779099</v>
+        <v>127774723</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3289,13 +3288,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568259</v>
+        <v>567958</v>
       </c>
       <c r="R25" t="n">
-        <v>7084847</v>
+        <v>7084872</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3322,24 +3321,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,57 +3338,66 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127777215</v>
+        <v>127775069</v>
       </c>
       <c r="B26" t="n">
-        <v>80188</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568021</v>
+        <v>567949</v>
       </c>
       <c r="R26" t="n">
-        <v>7084739</v>
+        <v>7084881</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3434,19 +3427,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,15 +3444,898 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127776971</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>567962</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7084778</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127777006</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>567977</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7084799</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127774340</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>567969</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7084911</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127778829</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>568221</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7084843</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127777166</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>568005</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7084751</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127778786</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>568210</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7084862</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127779820</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>568153</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7084763</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127774579</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>567972</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7084896</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24589-2025 artfynd.xlsx
+++ b/artfynd/A 24589-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127778779</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775120</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779918</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775305</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127777269</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779776</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775221</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127777215</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127778808</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774276</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,6 +1919,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774875</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1981,6 +2041,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774904</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2098,6 +2163,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127777308</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127777376</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2332,6 +2407,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127777452</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2449,6 +2529,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127778350</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2566,6 +2651,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127778496</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2683,6 +2773,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779099</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2800,6 +2895,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127780066</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2921,6 +3021,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127778509</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3028,6 +3133,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775383</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3245,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779879</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3241,6 +3356,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774278</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3347,6 +3467,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774723</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3453,6 +3578,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775069</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3569,6 +3699,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127776971</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3685,6 +3820,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127777006</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3792,6 +3932,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774340</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3899,6 +4044,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127778829</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4015,6 +4165,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127777166</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4122,6 +4277,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127778786</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4229,6 +4389,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127779820</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4336,8 +4501,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774579</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>